--- a/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
+++ b/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>3町共通の確認事項24件。特に認知症施策推進計画の策定主体（案B）と意見の聴取の方法。</t>
+          <t>3町共通の確認事項25件。特に認知症施策推進計画の策定主体（案B）と意見の聴取の方法。</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>35件（決着したものを除く）</t>
+          <t>36件（決着したものを除く）</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>東川町4件・美瑛町5件・東神楽町2件・3町共通24件</t>
+          <t>東川町4件・美瑛町5件・東神楽町2件・3町共通25件</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -2961,7 +2961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3739,8 +3739,38 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="9" t="n">
+        <v>169</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>(2)(6)</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度の評価指標の明細列299のうち78列で、構成3町の一部の町のみが得点している。3町は制度・保険者が同じであり条件がそろっているため、既に実施している町の取組を区域内に広げることで得点に結びつく余地がある。配点の大きいものは医療・介護関係者間の情報共有（東神楽町のみ得点）、介護人材の確保・定着の取組状況、認知症サポーター等を活用した地域支援体制の構築である。①区域内で取扱いをそろえる項目を選ぶか。②選ぶ場合、10月の町別協議で実施の可否を伺う対象としてよいか。</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>※ 特定の町へお伺いする事項は03〜05シートに掲げています。サービス見込量・給付費・保険料は保険者（広域連合）を単位として算定するため、町別には算定しません。</t>
         </is>
@@ -3749,7 +3779,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
+++ b/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
@@ -1302,7 +1302,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>東川+23・美瑛-15・東神楽+12</t>
+          <t>東川＋23・美瑛▲15・東神楽＋12</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>3町計の65歳以上は令和元年9,146人から令和7年9,232人（年+0.16％）でほぼ横ばいであるのに対し、85歳以上は1,743人から1,960人（年+1.97％）で増えています。</t>
+          <t>3町計の65歳以上は令和元年9,146人から令和7年9,232人（年＋0.16％）でほぼ横ばいであるのに対し、85歳以上は1,743人から1,960人（年＋1.97％）で増えています。</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>令和6年度から令和8年度にかけて、東川町は+23人、東神楽町は+12人と増える一方、美瑛町は-15人と減っています。</t>
+          <t>令和6年度から令和8年度にかけて、東川町は＋23人、東神楽町は＋12人と増える一方、美瑛町は▲15人と減っています。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>令和8年度は東川町315点・美瑛町308点・東神楽町379点で、最大の差は71点です。令和6年度からの動きも東川町-1点・美瑛町-4点・東神楽町+11点と分かれています。</t>
+          <t>令和8年度は東川町315点・美瑛町308点・東神楽町379点で、最大の差は71点です。令和6年度からの動きも東川町▲1点・美瑛町▲4点・東神楽町＋11点と分かれています。</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">

--- a/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
+++ b/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
@@ -761,7 +761,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>見込量・給付費・保険料はサービス見込量 第1次概算によります。</t>
+          <t>見込量・給付費・保険料はサービス見込量の算定によります。</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>本表（01・02・06シート）、計画素案、サービス見込量 第1次概算、町別データシート</t>
+          <t>本表（01・02・06シート）、計画素案、サービス見込量の算定、町別データシート</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算／在宅生活改善調査</t>
+          <t>サービス見込量の算定／在宅生活改善調査</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算／北海道 特別養護老人ホーム名簿</t>
+          <t>サービス見込量の算定／北海道 特別養護老人ホーム名簿</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算／介護保険事業計画作成支援ツール</t>
+          <t>サービス見込量の算定／介護保険事業計画作成支援ツール</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算／北海道の指定事業所一覧</t>
+          <t>サービス見込量の算定／北海道の指定事業所一覧</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>区域内定員62人のうち43人が美瑛町にある。サービス見込量 第1次概算では令和11年度に定員の99.9％に達し、令和12年度には定員を超えると見込まれる。第10期の整備方針を伺いたい。確認事項No.88（必要利用定員総数）と一体のものである。</t>
+          <t>区域内定員62人のうち43人が美瑛町にある。サービス見込量の算定では令和11年度に定員の99.9％に達し、令和12年度には定員を超えると見込まれる。第10期の整備方針を伺いたい。確認事項No.88（必要利用定員総数）と一体のものである。</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求めている。第9期計画には当該記載がないため、第10期計画に新たに設ける（計画素案 第6章第4節4）。①基盤整備単位としての日常生活圏域を3町（3圏域）とすることでよいか（統計・分析単位は第9期の6圏域を維持する。計画素案 第1章第7節）。②認知症対応型共同生活介護の圏域別の定員をご確認いただきたい。北海道の名簿では7事業所108人＋［要確認］、見える化システムD26（令和6年度）では5事業所99人であり一致しない。③令和9〜11年度の必要利用定員総数は3町の整備方針の確定後に定める。サービス見込量 第1次概算（9月26日）より前に①の決定をいただきたい。</t>
+          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求めている。第9期計画には当該記載がないため、第10期計画に新たに設ける（計画素案 第6章第4節4）。①基盤整備単位としての日常生活圏域を3町（3圏域）とすることでよいか（統計・分析単位は第9期の6圏域を維持する。計画素案 第1章第7節）。②認知症対応型共同生活介護の圏域別の定員をご確認いただきたい。北海道の名簿では7事業所108人＋［要確認］、見える化システムD26（令和6年度）では5事業所99人であり一致しない。③令和9〜11年度の必要利用定員総数は3町の整備方針の確定後に定める。サービス見込量の算定（9月26日）より前に①の決定をいただきたい。</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">

--- a/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
+++ b/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
@@ -3250,7 +3250,7 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
+          <t>社会資源一覧の従業員数は施設単位の実人数を用い、延べの値は用いない（同一の施設が複数のサービスで登録されている分を除く）。介護人材実態調査の採用者数・離職者数も同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">

--- a/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
+++ b/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>3町共通の確認事項25件。特に認知症施策推進計画の策定主体（案B）と意見の聴取の方法。</t>
+          <t>3町共通の確認事項26件。特に認知症施策推進計画の策定主体（案B）と意見の聴取の方法。</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>36件（決着したものを除く）</t>
+          <t>37件（決着したものを除く）</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>東川町4件・美瑛町5件・東神楽町2件・3町共通25件</t>
+          <t>東川町4件・美瑛町5件・東神楽町2件・3町共通26件</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -2961,7 +2961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3769,8 +3769,38 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>令和8年9月18日の社会保障審議会介護保険部会において、全市町村が令和10年4月1日までに介護保険事務システムから介護情報基盤へのデータ移行を含めて完了し、介護情報基盤の活用を開始することを目指すこととされました（標準化対応の適合基準日は令和9年1月1日）。構成3町における①介護保険事務システムの標準化対応の状況、②介護情報基盤へデータを送信するためのシステムの改修の予定、③データ移行の予定をお示しいただきたい。あわせて、ケアプランデータ連携機能が令和9年1月に介護情報基盤へ統合され、以後は新システム（介護保険資格確認等WEBサービス）での事業所及び管理者の登録を要することとなるため、区域内の事業所への周知をどこが行うかをお決めいただきたい。</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>の当方の扱い＝国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>※ 特定の町へお伺いする事項は03〜05シートに掲げています。サービス見込量・給付費・保険料は保険者（広域連合）を単位として算定するため、町別には算定しません。</t>
         </is>
@@ -3778,8 +3808,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
+++ b/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>3町共通の確認事項26件。特に認知症施策推進計画の策定主体（案B）と意見の聴取の方法。</t>
+          <t>3町共通の確認事項29件。特に認知症施策推進計画の策定主体（案B）と意見の聴取の方法。</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>37件（決着したものを除く）</t>
+          <t>40件（決着したものを除く）</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>東川町4件・美瑛町5件・東神楽町2件・3町共通26件</t>
+          <t>東川町4件・美瑛町5件・東神楽町2件・3町共通29件</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -2961,7 +2961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3799,8 +3799,98 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="9" t="n">
+        <v>178</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>(1)(6)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>老人福祉法第20条の8は市町村老人福祉計画を定めるものとし、同計画は市町村介護保険事業計画と一体のものとして作成することとされています。構成3町の高齢者福祉計画がこれに当たるものと考えられますが、当方は同法の条文及び3町の計画書を確認していません。①構成3町の高齢者福祉計画が老人福祉法による市町村老人福祉計画に当たるか（計画の名称及び根拠条文）。②一体のものとして作成する方法（同一の冊子とするか、本計画と3町の計画を別冊としたうえで共通KPIと役割分担により接続するか）。③3町の計画における老人福祉事業の量の目標の定め方と、本計画のサービス見込量との関係。</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>の当方の扱い＝構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="9" t="n">
+        <v>179</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>(1)(6)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>成年後見制度の利用の促進に関する法律第14条は、国の基本計画を勘案して、市町村が成年後見制度の利用の促進に関する施策についての基本的な計画を定めるよう努めるものとしています。同法は市町村を名宛人としており、市町村認知症施策推進計画と同じ構造であると考えられます。①構成3町における同計画の策定の状況（策定済みか、高齢者福祉計画又は地域福祉計画の中に位置づけているか）。②中核機関の整備の状況及び権利擁護支援の地域連携ネットワークの構成（第5章 基本目標1の代表KPIの基準値に関わります）。③本計画における記載の範囲（3町の計画との役割分担）。</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>の当方の扱い＝同計画は構成3町が定めるものとして計画素案に記載し、本計画は介護保険法第117条第3項による権利擁護の施策（第5章 基本目標1）をもって接続する。中核機関の整備の状況は［要確認］として残す</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="9" t="n">
+        <v>180</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>(1)(6)</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道第9期計画の評価指標⑦は「避難確保計画を作成した施設」を指標としており、当方はこれを施設数の実数により用いる整理としています（計画素案 第1章第8節）。①構成3町の地域防災計画において要配慮者利用施設として定められている介護保険施設・事業所の一覧。②避難確保計画の作成及び避難訓練の実施の状況（施設数）。③第10期の目標値の置き方（全施設作成とするか）。</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>の当方の扱い＝対象施設及び作成の状況を［要確認］として残し、第5章 基本目標5の主な事業に作成及び避難訓練の確認を置くにとどめ、達成目標に数値を掲げない。避難確保計画はBCPとは別の計画であり、BCPの策定率をもって作成の状況としない</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>※ 特定の町へお伺いする事項は03〜05シートに掲げています。サービス見込量・給付費・保険料は保険者（広域連合）を単位として算定するため、町別には算定しません。</t>
         </is>
@@ -3808,8 +3898,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A34:F34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
+++ b/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>3町共通の確認事項29件。特に認知症施策推進計画の策定主体（案B）と意見の聴取の方法。</t>
+          <t>3町共通の確認事項30件。特に認知症施策推進計画の策定主体（案B）と意見の聴取の方法。</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>40件（決着したものを除く）</t>
+          <t>41件（決着したものを除く）</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>東川町4件・美瑛町5件・東神楽町2件・3町共通29件</t>
+          <t>東川町4件・美瑛町5件・東神楽町2件・3町共通30件</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -2961,7 +2961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3889,8 +3889,38 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="9" t="n">
+        <v>184</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>(3)(4)(5)</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>介護給付費分科会第270回において、短期入所生活介護について31日以上連続して利用する場合の評価の見直しと、積雪期・猛暑期・農繁期等の季節利用に係る例外が検討されていると社内の記録にあります（原本は未確認。No.182）。当広域連合は積雪地であり、健康とくらしの調査では生活動作の困りごととして除雪を挙げた方が回答者の24.3％と最も多くなっています。①区域内の短期入所生活介護事業所における季節による利用の変動（積雪期の利用日数・緊急受入・断り件数）。②31日以上連続して利用している方の人数と長期化の理由（居住の代替としての利用か、季節的な利用か）。③事業所への照会を行うかどうか、様式を当方で用意するか。</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>の当方の扱い＝令和7年度（12か月の完結年度）の実績により短期入所生活介護の見込量を算定し、季節補正を行わない（基準年度が完結年度であるため年度換算係数は1.0000となり効きは0円である）。季節利用の例外が示された時点で利用日数の置き方を確かめる</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>※ 特定の町へお伺いする事項は03〜05シートに掲げています。サービス見込量・給付費・保険料は保険者（広域連合）を単位として算定するため、町別には算定しません。</t>
         </is>
@@ -3899,7 +3929,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
+++ b/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>介護給付費分科会第270回において、短期入所生活介護について31日以上連続して利用する場合の評価の見直しと、積雪期・猛暑期・農繁期等の季節利用に係る例外が検討されていると社内の記録にあります（原本は未確認。No.182）。当広域連合は積雪地であり、健康とくらしの調査では生活動作の困りごととして除雪を挙げた方が回答者の24.3％と最も多くなっています。①区域内の短期入所生活介護事業所における季節による利用の変動（積雪期の利用日数・緊急受入・断り件数）。②31日以上連続して利用している方の人数と長期化の理由（居住の代替としての利用か、季節的な利用か）。③事業所への照会を行うかどうか、様式を当方で用意するか。</t>
+          <t>介護給付費分科会第270回 資料4において、短期入所生活介護について31日以上連続して利用する場合の減算を61日以上連続して利用する場合と同程度に改めることと、積雪期・猛暑期・農繁期等の季節による利用のみの方について例外的に当該減算を適用しない仕組みを設けることの双方が検討されています。同資料は「中山間地域では冬期間のみ利用することで在宅生活の継続を図る事例がみられるなど、人口規模が小さい自治体においては、積雪期や農繁期等の季節利用ニーズへの対応として短期入所生活介護が活用されている実態が把握された」としています（令和8年10月14日に原典により確認）。また同資料5において、短期入所療養介護にも長期利用に係る減算を新たに設けることが検討されています。当広域連合は積雪地であり、健康とくらしの調査では生活動作の困りごととして除雪を挙げた方が回答者の24.3％と最も多くなっています。①区域内の短期入所生活介護事業所における季節による利用の変動（積雪期の利用日数・緊急受入・断り件数）。②31日以上連続して利用している方の人数と長期化の理由（居住の代替としての利用か、季節的な利用か）。③事業所への照会を行うかどうか、様式を当方で用意するか。例外の対象となるには季節による利用のみであることを示す必要が生じる可能性があります。</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">

--- a/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
+++ b/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>3町共通の確認事項30件。特に認知症施策推進計画の策定主体（案B）と意見の聴取の方法。</t>
+          <t>3町共通の確認事項31件。特に認知症施策推進計画の策定主体（案B）と意見の聴取の方法。</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>41件（決着したものを除く）</t>
+          <t>42件（決着したものを除く）</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>東川町4件・美瑛町5件・東神楽町2件・3町共通30件</t>
+          <t>東川町4件・美瑛町5件・東神楽町2件・3町共通31件</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -2961,7 +2961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3919,8 +3919,38 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="9" t="n">
+        <v>185</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>(5)(6)</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>社会福祉法等の一部を改正する法律案要綱 第1の4（3）により、小規模市町村（その人口規模、その人口の減少の状況等からみて福祉サービスを提供する体制の確保に支障を生じ、又は生ずるおそれがあると認められる市町村として厚生労働省令で定める基準に該当するもの）は、社会福祉法に基づく事業及び関係法律に基づく事業を一体のものとして実施することにより、包括的な支援体制を一体的に整備する事業を行うことができることとされました（社会福祉法第106条の6。施行は令和9年4月1日）。費用は小規模市町村の支弁とし、国及び都道府県が交付金を交付します。実施する場合は、関係法律に基づく事業についての市町村の支弁に係る費用から当該事業の実施に要する費用を除くこととされています（同法第106条の12）。①構成3町が厚生労働省令で定める基準に該当するかどうか。②「関係法律に基づく事業」に介護保険法の包括的支援事業（地域包括支援センターの運営）が含まれるかどうか。③含まれる場合、当該費用が本広域連合の地域支援事業費（B）から除かれるかどうか。地域支援事業費は保険料収納必要額の算定の基礎であるため、除かれる場合は保険料を下げる向きに働きます。</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>の当方の扱い＝現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>※ 特定の町へお伺いする事項は03〜05シートに掲げています。サービス見込量・給付費・保険料は保険者（広域連合）を単位として算定するため、町別には算定しません。</t>
         </is>
@@ -3928,8 +3958,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
+++ b/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
@@ -3820,7 +3820,7 @@
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>の当方の扱い＝構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
+          <t>の当方の扱い＝構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない【令和8年10月15日】参照条文により、介護保険法第117条第7項が「老人福祉法第20条の8第1項に規定する市町村老人福祉計画と一体のものとして作成されなければならない」ことを定めていることを確かめた。条及び項は第20条の8第1項である。老人福祉法そのものの条文は参照条文に収録されていない（第18条及び第20条の6のみ）ため、同条の内容及び市町村老人福祉計画の記載事項はなお確認できていない</t>
         </is>
       </c>
       <c r="F31" s="14" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>の当方の扱い＝現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
+          <t>の当方の扱い＝現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する【令和8年10月15日】参照条文には社会福祉法第106条の3（包括的な支援体制の整備）までが収録されており、第106条の6は改正法により新設される規定であるため現れない。本件は進んでいない</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr">

--- a/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
+++ b/output/第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx
@@ -2755,7 +2755,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>区域内定員62人のうち43人が美瑛町にある。サービス見込量の算定では令和11年度に定員の99.9％に達し、令和12年度には定員を超えると見込まれる。第10期の整備方針を伺いたい。確認事項No.88（必要利用定員総数）と一体のものである。</t>
+          <t>区域内定員62人のうち42人が美瑛町にある（地域密着型介護老人福祉施設 美瑛慈光園24人、美瑛慈光園サテライト特養 燈18人。北海道 特別養護老人ホーム名簿令和8年9月1日現在）。サービス見込量の算定では令和11年度に定員の99.9％に達し、令和12年度には定員を超えると見込まれる。第10期の整備方針を伺いたい。確認事項No.88（必要利用定員総数）と一体のものである。</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
